--- a/docs/calibration/figures/n114_shmtrace/tables.xlsx
+++ b/docs/calibration/figures/n114_shmtrace/tables.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Run" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Samples" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Variants" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Positional" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Spectrum" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variants" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Positional" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spectrum" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO7"/>
+  <dimension ref="A1:AP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -595,19 +595,20 @@
     <col width="19" customWidth="1" min="26" max="26"/>
     <col width="28" customWidth="1" min="27" max="27"/>
     <col width="25" customWidth="1" min="28" max="28"/>
-    <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="25" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="30" max="30"/>
+    <col width="25" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="17" customWidth="1" min="33" max="33"/>
     <col width="11" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="19" customWidth="1" min="36" max="36"/>
-    <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
-    <col width="11" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="19" customWidth="1" min="37" max="37"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,65 +754,70 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>mutation_frequency_observed_x1e3</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>mutated_reads_pct</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pct_GC</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pct_transitions</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pct_CT_GA</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>s5f_index</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>s5f_p</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>pct_AT_in_WA_TW</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>analysed_bp</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>null_from</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>model_used</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>warnings</t>
         </is>
@@ -838,19 +844,19 @@
         <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>23.262</v>
+        <v>23.264</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3323</v>
+        <v>0.332348</v>
       </c>
       <c r="H2" t="n">
-        <v>31.035</v>
+        <v>31.178</v>
       </c>
       <c r="I2" t="n">
-        <v>26.964</v>
+        <v>27.595</v>
       </c>
       <c r="J2" t="n">
-        <v>35.102</v>
+        <v>35.777</v>
       </c>
       <c r="K2" t="n">
         <v>52</v>
@@ -859,19 +865,19 @@
         <v>22</v>
       </c>
       <c r="M2" t="n">
-        <v>3.933</v>
+        <v>3.606</v>
       </c>
       <c r="N2" t="n">
-        <v>23.39</v>
+        <v>23.81</v>
       </c>
       <c r="O2" t="n">
-        <v>7.773</v>
+        <v>7.913</v>
       </c>
       <c r="P2" t="n">
-        <v>3.702</v>
+        <v>4.331</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.84</v>
+        <v>12.513</v>
       </c>
       <c r="W2" t="n">
         <v>11</v>
@@ -880,40 +886,43 @@
         <v>1.3333</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.3626</v>
+      </c>
+      <c r="AD2" t="n">
         <v>50.2</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.82</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>94.3</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>54.3</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>52.9</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>77.3</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>25</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>615</v>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>C3+C4+D1</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>11 calls fall in 9 bp at 98-106 (p = 2.2e-05); check the spectrum there before counting them as mutations</t>
         </is>
@@ -940,19 +949,19 @@
         <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>16.247</v>
+        <v>16.246</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3316</v>
+        <v>0.331542</v>
       </c>
       <c r="H3" t="n">
-        <v>32.912</v>
+        <v>32.909</v>
       </c>
       <c r="I3" t="n">
-        <v>27.5</v>
+        <v>27.979</v>
       </c>
       <c r="J3" t="n">
-        <v>38.326</v>
+        <v>38.84</v>
       </c>
       <c r="K3" t="n">
         <v>35</v>
@@ -967,13 +976,13 @@
         <v>50.26</v>
       </c>
       <c r="O3" t="n">
-        <v>16.665</v>
+        <v>16.663</v>
       </c>
       <c r="P3" t="n">
-        <v>11.253</v>
+        <v>11.733</v>
       </c>
       <c r="Q3" t="n">
-        <v>22.079</v>
+        <v>22.595</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -982,40 +991,43 @@
         <v>0.5789</v>
       </c>
       <c r="AC3" t="n">
+        <v>0.5901</v>
+      </c>
+      <c r="AD3" t="n">
         <v>25.2</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>0.356</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>98</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>49</v>
       </c>
       <c r="AG3" t="n">
         <v>49</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AH3" t="n">
+        <v>49</v>
+      </c>
+      <c r="AK3" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
       <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
         <v>615</v>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>C3+C4+D1</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1038,19 +1050,19 @@
         <v>173</v>
       </c>
       <c r="F4" t="n">
-        <v>57.455</v>
+        <v>57.456</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3321</v>
+        <v>0.332113</v>
       </c>
       <c r="H4" t="n">
-        <v>66.98</v>
+        <v>67.253</v>
       </c>
       <c r="I4" t="n">
-        <v>62.676</v>
+        <v>63.437</v>
       </c>
       <c r="J4" t="n">
-        <v>71.288</v>
+        <v>72.065</v>
       </c>
       <c r="K4" t="n">
         <v>112</v>
@@ -1059,19 +1071,19 @@
         <v>27</v>
       </c>
       <c r="M4" t="n">
-        <v>3.936</v>
+        <v>3.28</v>
       </c>
       <c r="N4" t="n">
-        <v>28.68</v>
+        <v>29.5</v>
       </c>
       <c r="O4" t="n">
-        <v>9.525</v>
+        <v>9.797000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>5.221</v>
+        <v>5.981</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.832</v>
+        <v>14.61</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1080,40 +1092,43 @@
         <v>2.8163</v>
       </c>
       <c r="AC4" t="n">
+        <v>2.8761</v>
+      </c>
+      <c r="AD4" t="n">
         <v>78.8</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>1.732</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>96.5</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>52.6</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>52</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>61.7</v>
       </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
       <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
         <v>615</v>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>C3+C4+D1</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1139,7 +1154,7 @@
         <v>0.327</v>
       </c>
       <c r="G5" t="n">
-        <v>0.327</v>
+        <v>0.326996</v>
       </c>
       <c r="H5" t="n">
         <v>0.327</v>
@@ -1148,7 +1163,7 @@
         <v>0.327</v>
       </c>
       <c r="J5" t="n">
-        <v>2.403</v>
+        <v>2.819</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -1166,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.073</v>
+        <v>-1.972</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.076</v>
+        <v>2.492</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1178,37 +1193,40 @@
         <v>0.0065</v>
       </c>
       <c r="AC5" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0.4</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>0.004</v>
       </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
         <v>100</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AM5" t="n">
         <v>615</v>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>C4+D1</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1234,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3268</v>
+        <v>0.326827</v>
       </c>
       <c r="H6" t="n">
         <v>0.628</v>
@@ -1243,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.759</v>
+        <v>3.196</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1261,10 +1279,10 @@
         <v>0.628</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.503</v>
+        <v>-1.337</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.759</v>
+        <v>3.196</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1278,20 +1296,23 @@
       <c r="AD6" t="n">
         <v>0</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
         <v>615</v>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>C3+D1</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1317,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3266</v>
+        <v>0.326648</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1326,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.261</v>
+        <v>1.62</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1344,10 +1365,10 @@
         <v>-0.634</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.531</v>
+        <v>-2.512</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.261</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1361,20 +1382,23 @@
       <c r="AD7" t="n">
         <v>0</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>615</v>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>C3+C4</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>quality_calibrated</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1387,7 +1411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB3"/>
+  <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1399,9 +1423,9 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="28" customWidth="1" min="15" max="15"/>
@@ -1418,8 +1442,8 @@
     <col width="28" customWidth="1" min="26" max="26"/>
     <col width="28" customWidth="1" min="27" max="27"/>
     <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="24" customWidth="1" min="29" max="29"/>
-    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="28" customWidth="1" min="29" max="29"/>
+    <col width="28" customWidth="1" min="30" max="30"/>
     <col width="28" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
     <col width="28" customWidth="1" min="33" max="33"/>
@@ -1428,22 +1452,32 @@
     <col width="28" customWidth="1" min="36" max="36"/>
     <col width="28" customWidth="1" min="37" max="37"/>
     <col width="28" customWidth="1" min="38" max="38"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="24" customWidth="1" min="39" max="39"/>
+    <col width="22" customWidth="1" min="40" max="40"/>
     <col width="28" customWidth="1" min="41" max="41"/>
     <col width="28" customWidth="1" min="42" max="42"/>
-    <col width="27" customWidth="1" min="43" max="43"/>
-    <col width="22" customWidth="1" min="44" max="44"/>
-    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="28" customWidth="1" min="43" max="43"/>
+    <col width="28" customWidth="1" min="44" max="44"/>
+    <col width="28" customWidth="1" min="45" max="45"/>
     <col width="28" customWidth="1" min="46" max="46"/>
     <col width="28" customWidth="1" min="47" max="47"/>
     <col width="28" customWidth="1" min="48" max="48"/>
-    <col width="24" customWidth="1" min="49" max="49"/>
-    <col width="22" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="11" customWidth="1" min="50" max="50"/>
     <col width="28" customWidth="1" min="51" max="51"/>
     <col width="28" customWidth="1" min="52" max="52"/>
-    <col width="28" customWidth="1" min="53" max="53"/>
-    <col width="15" customWidth="1" min="54" max="54"/>
+    <col width="27" customWidth="1" min="53" max="53"/>
+    <col width="22" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="28" customWidth="1" min="56" max="56"/>
+    <col width="28" customWidth="1" min="57" max="57"/>
+    <col width="28" customWidth="1" min="58" max="58"/>
+    <col width="24" customWidth="1" min="59" max="59"/>
+    <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="28" customWidth="1" min="61" max="61"/>
+    <col width="28" customWidth="1" min="62" max="62"/>
+    <col width="28" customWidth="1" min="63" max="63"/>
+    <col width="15" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1484,235 +1518,285 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>unique_density_x1e5_sensitivity_p_welch_log_half_event_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unique_density_x1e5_sensitivity_p_welch_log_third_of_smallest_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>unique_density_x1e5_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_sd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_p_welch_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_p_welch_log_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>combined_density_x1e5_sensitivity_p_welch_log_half_event_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>combined_density_x1e5_sensitivity_p_welch_log_third_of_smallest_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>combined_density_x1e5_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_sd</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_p_welch_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_p_welch_log_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>single_read_density_x1e5_sensitivity_p_welch_log_half_event_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>single_read_density_x1e5_sensitivity_p_welch_log_third_of_smallest_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>single_read_density_x1e5_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_mean</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_sd</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_p_welch_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_p_welch_log_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>clone_weighted_frequency_x1e3_sensitivity_p_welch_log_half_event_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>clone_weighted_frequency_x1e3_sensitivity_p_welch_log_third_of_smallest_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>clone_weighted_frequency_x1e3_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_mean</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_sd</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_p_welch_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_p_welch_log_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>mutation_frequency_x1e3_sensitivity_p_welch_log_half_event_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>mutation_frequency_x1e3_sensitivity_p_welch_log_third_of_smallest_vs_pMX-Empty</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
         <is>
           <t>mutation_frequency_x1e3_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_sd</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_p_welch_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_p_welch_log_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>mutated_reads_pct_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_mean</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_sd</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_p_welch_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_p_welch_log_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>mean_mutations_per_read_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>pct_GC_mean</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>pct_GC_sd</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>pct_GC_p_welch_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>pct_GC_p_welch_log_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>pct_GC_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>pct_transitions_mean</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>pct_transitions_sd</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>pct_transitions_p_welch_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>pct_transitions_p_welch_log_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>pct_transitions_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_mean</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_sd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_p_welch_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_p_welch_log_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>pct_GC_in_WRC_GYW_p_mwu_vs_pMX-Empty</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>compared_with</t>
         </is>
@@ -1731,120 +1815,144 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>32.3213</v>
+        <v>32.322</v>
       </c>
       <c r="E2" t="n">
-        <v>22.0472</v>
+        <v>22.0477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1270511514957733</v>
+        <v>0.1270517870020959</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007064935705445034</v>
+        <v>0.007065640246490911</v>
       </c>
       <c r="H2" t="n">
+        <v>0.0009586730567344013</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0005932174096485131</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.07652250047505924</v>
       </c>
-      <c r="I2" t="n">
-        <v>43.6423</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20.2328</v>
-      </c>
       <c r="K2" t="n">
-        <v>0.06559032930283434</v>
+        <v>43.78</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001667918349607397</v>
+        <v>20.3466</v>
       </c>
       <c r="M2" t="n">
+        <v>0.06588044827760005</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0001676879552735612</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001047641118098609</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.003599069211743108</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.1</v>
       </c>
-      <c r="N2" t="n">
-        <v>11.321</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4.7102</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.05083489903522587</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.0004912947561413202</v>
-      </c>
       <c r="R2" t="n">
+        <v>11.4577</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.6053</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.04749973117975179</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0004504428023553188</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.005402548177315321</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.002499807923445312</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.1</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AF2" t="n">
         <v>1.5762</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AG2" t="n">
         <v>1.1383</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AH2" t="n">
         <v>0.1389108675235802</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AI2" t="n">
+        <v>0.001607219852295179</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.0006661275161478677</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.0006352139464301282</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.07652250047505924</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>26.8201</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.08037147928709994</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.0003944153161700952</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.07652250047505924</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.9693000000000001</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.1389114996153989</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.0006355577384626653</v>
       </c>
       <c r="AL2" t="n">
         <v>0.07652250047505924</v>
       </c>
       <c r="AM2" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>26.8201</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.08037147928709994</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.0003995634025608049</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.07652250047505924</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.1389114996153989</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.001604775891494914</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.07652250047505924</v>
+      </c>
+      <c r="AW2" t="n">
         <v>96.2667</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AX2" t="n">
         <v>1.861</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="BA2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BB2" t="n">
         <v>51.9667</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="BC2" t="n">
         <v>2.7062</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BF2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="BG2" t="n">
         <v>72.0333</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BH2" t="n">
         <v>8.9495</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>pMX-Empty</t>
         </is>
@@ -1868,43 +1976,43 @@
       <c r="E3" t="n">
         <v>0.1888</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.3183</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.3141</v>
       </c>
-      <c r="N3" t="n">
+      <c r="R3" t="n">
         <v>-0.002</v>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
         <v>0.631</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AF3" t="n">
         <v>0.0022</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AG3" t="n">
         <v>0.0038</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AM3" t="n">
         <v>0.1333</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AN3" t="n">
         <v>0.2309</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AR3" t="n">
         <v>0.0013</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AS3" t="n">
         <v>0.0023</v>
       </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
